--- a/attachments/DSJ_AE_Empirical_Studies_in_SCM.xlsx
+++ b/attachments/DSJ_AE_Empirical_Studies_in_SCM.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\New\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D48D1D-EF67-4021-9323-1DBEDFC7F00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="16400"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -18,25 +12,20 @@
   <definedNames>
     <definedName name="Z_C5A7EE99_A930_471B_BD26_7D28F82FE1E9_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$38</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
   <customWorkbookViews>
     <customWorkbookView name="Filter 1" guid="{C5A7EE99-A930-471B-BD26-7D28F82FE1E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="SycmCUo6HNunQlwyrex2ggxbzQ/Kv6hJceRGnQKeulM="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -44,6 +33,7 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <scheme val="minor"/>
+            <charset val="1"/>
           </rPr>
           <t>======
 ID#AAABubxlAIo
@@ -53,16 +43,11 @@
       </text>
     </comment>
   </commentList>
-  <extLst>
-    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mg7CUCo8ZTbQW6AByhIH7imwY2M4w=="/>
-    </ext>
-  </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="420">
   <si>
     <t>First Name</t>
   </si>
@@ -100,6 +85,9 @@
     <t>Topical Area Of Expertise (4)</t>
   </si>
   <si>
+    <t>DSJ Empirical Studies in SCM AEs</t>
+  </si>
+  <si>
     <t>Gopesh</t>
   </si>
   <si>
@@ -115,6 +103,9 @@
     <t>University of Illinois at Urbana Champaign</t>
   </si>
   <si>
+    <t>Empirical Studies in Supply Chain Management</t>
+  </si>
+  <si>
     <t>Quantitative Empirical Methods</t>
   </si>
   <si>
@@ -874,6 +865,9 @@
     <t>Supply Chain Finance</t>
   </si>
   <si>
+    <t>Editorial Review Board Members</t>
+  </si>
+  <si>
     <t>Baichun</t>
   </si>
   <si>
@@ -889,9 +883,6 @@
     <t>Webster University</t>
   </si>
   <si>
-    <t>Empirical Studies in Supply Chain Management</t>
-  </si>
-  <si>
     <t>Yoon Kim</t>
   </si>
   <si>
@@ -1303,21 +1294,37 @@
     <t>Social Dilemmas</t>
   </si>
   <si>
-    <t>DSJ Empirical Studies in SCM AEs</t>
-  </si>
-  <si>
-    <t>Editorial Review Board Members</t>
+    <t>Kedong</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>chenk16@rpi.edu</t>
+  </si>
+  <si>
+    <t>Lally School of Management</t>
+  </si>
+  <si>
+    <t>Rensselaer Polytechnic Institute</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="33">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1325,80 +1332,425 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Verdana"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans&quot;"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1408,57 +1760,343 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="41" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1656,2175 +2294,2190 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P1001"/>
-  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6071428571429" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.27734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" customWidth="1"/>
-    <col min="3" max="4" width="30.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.71875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="56.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="56.38671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="53.71875" style="2" customWidth="1"/>
-    <col min="9" max="12" width="46.5" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="12.609375" style="2"/>
+    <col min="1" max="1" width="28.2767857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="4" width="30.1071428571429" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7232142857143" style="1" customWidth="1"/>
+    <col min="6" max="6" width="56.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="56.3839285714286" style="1" customWidth="1"/>
+    <col min="8" max="8" width="53.7232142857143" style="1" customWidth="1"/>
+    <col min="9" max="12" width="46.5" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.6071428571429" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A17" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A19" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A20" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A22" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A23" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A24" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A25" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A26" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A27" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A28" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A29" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A31" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A32" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A33" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A34" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A35" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A36" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A38" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+    </row>
+    <row r="39" ht="14" spans="1:16">
+      <c r="A39" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" ht="14" spans="1:16">
+      <c r="A40" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="P40" s="13"/>
+    </row>
+    <row r="41" ht="14" spans="1:16">
+      <c r="A41" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="P41" s="14"/>
+    </row>
+    <row r="42" ht="14" spans="1:16">
+      <c r="A42" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="P42" s="5"/>
+    </row>
+    <row r="43" ht="14" spans="1:12">
+      <c r="A43" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" ht="14" spans="1:12">
+      <c r="A44" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="45" ht="14" spans="1:12">
+      <c r="A45" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" ht="14" spans="1:12">
+      <c r="A46" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" ht="14" spans="1:12">
+      <c r="A47" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" ht="14" spans="1:12">
+      <c r="A48" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" ht="14" spans="1:12">
+      <c r="A49" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" ht="14" spans="1:12">
+      <c r="A50" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="51" ht="14" spans="1:12">
+      <c r="A51" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" ht="14" spans="1:12">
+      <c r="A52" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" ht="14" spans="1:12">
+      <c r="A53" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" ht="14" spans="1:12">
+      <c r="A54" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" ht="14" spans="1:12">
+      <c r="A55" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="56" ht="14" spans="1:12">
+      <c r="A56" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="L56" s="12"/>
+    </row>
+    <row r="57" ht="14" spans="1:12">
+      <c r="A57" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" ht="14" spans="1:12">
+      <c r="A58" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" ht="14" spans="1:12">
+      <c r="A59" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="K59" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L30" s="4"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A38" s="14" t="s">
+      <c r="L59" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-    </row>
-    <row r="39" spans="1:16" ht="14.4">
-      <c r="A39" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="P39" s="4"/>
-    </row>
-    <row r="40" spans="1:16" ht="14.4">
-      <c r="A40" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="P40" s="9"/>
-    </row>
-    <row r="41" spans="1:16" ht="14.4">
-      <c r="A41" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="P41" s="10"/>
-    </row>
-    <row r="42" spans="1:16" ht="14.4">
-      <c r="A42" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L42" s="4"/>
-      <c r="P42" s="4"/>
-    </row>
-    <row r="43" spans="1:16" ht="14.4">
-      <c r="A43" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="L43" s="4"/>
-    </row>
-    <row r="44" spans="1:16" ht="14.4">
-      <c r="A44" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="14.4">
-      <c r="A45" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="14.4">
-      <c r="A46" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="L46" s="4"/>
-    </row>
-    <row r="47" spans="1:16" ht="14.4">
-      <c r="A47" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="14.4">
-      <c r="A48" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="14.4">
-      <c r="A49" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="14.4">
-      <c r="A50" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="14.4">
-      <c r="A51" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="14.4">
-      <c r="A52" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="L52" s="4"/>
-    </row>
-    <row r="53" spans="1:12" ht="14.4">
-      <c r="A53" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="L53" s="4"/>
-    </row>
-    <row r="54" spans="1:12" ht="14.4">
-      <c r="A54" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:12" ht="14.4">
-      <c r="A55" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="14.4">
-      <c r="A56" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="L56" s="8"/>
-    </row>
-    <row r="57" spans="1:12" ht="14.4">
-      <c r="A57" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="L57" s="4"/>
-    </row>
-    <row r="58" spans="1:12" ht="14.4">
-      <c r="A58" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="L58" s="4"/>
-    </row>
-    <row r="59" spans="1:12" ht="14.4">
-      <c r="A59" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:12" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -4766,12 +5419,8 @@
   <customSheetViews>
     <customSheetView guid="{C5A7EE99-A930-471B-BD26-7D28F82FE1E9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L37" xr:uid="{DA5AA236-54CC-4BF2-A179-1CC9B7FC9AE1}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="483439641"/>
-        </ext>
-      </extLst>
+      <headerFooter/>
+      <autoFilter ref="A1:L37"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="3">
@@ -4780,11 +5429,13 @@
     <mergeCell ref="K56:L56"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C13" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C13" r:id="rId3" display="hsiaohui@nccu.edu.tw"/>
+    <hyperlink ref="C60" r:id="rId4" display="chenk16@rpi.edu"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <pageSetup paperSize="1" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>